--- a/Data/uncertainty/hp.xlsx
+++ b/Data/uncertainty/hp.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12255"/>
+    <workbookView windowWidth="20752" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,13 +77,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -551,148 +544,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1047,19 +1040,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19.858407079646" customWidth="1"/>
     <col min="3" max="3" width="20.5840707964602" customWidth="1"/>
     <col min="4" max="4" width="18.1946902654867" customWidth="1"/>
-    <col min="8" max="8" width="12.7964601769912"/>
-    <col min="9" max="9" width="9.53097345132743"/>
-    <col min="10" max="12" width="12.7964601769912"/>
-    <col min="13" max="13" width="13.0176991150442" customWidth="1"/>
+    <col min="8" max="9" width="12.7964601769912"/>
+    <col min="10" max="10" width="9.53097345132743"/>
+    <col min="11" max="14" width="12.7964601769912"/>
+    <col min="15" max="16" width="13.0176991150442" customWidth="1"/>
+    <col min="17" max="17" width="12.7964601769912"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:17">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1069,26 +1063,29 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1"/>
+      <c r="M1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1"/>
+      <c r="O1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1"/>
+      <c r="Q1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1109,30 +1106,46 @@
         <v>226.836514285714</v>
       </c>
       <c r="I2">
+        <f ca="1">H2*1.3</f>
+        <v>294.887468571428</v>
+      </c>
+      <c r="J2">
         <v>0.969885</v>
       </c>
-      <c r="J2">
-        <f ca="1">H2*I2</f>
+      <c r="K2">
+        <f ca="1">H2*J2</f>
         <v>220.005332658</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <f ca="1">OFFSET($C$2,(ROW(C1)-1)*4,0)</f>
         <v>215.361904383375</v>
       </c>
-      <c r="L2">
+      <c r="M2">
+        <f ca="1">L2*1.3</f>
+        <v>279.970475698387</v>
+      </c>
+      <c r="N2">
         <f ca="1">OFFSET($D$2,(ROW(D1)-1)*4,0)</f>
         <v>238.311124188054</v>
       </c>
-      <c r="M2">
-        <f ca="1">IF(OR(J2&gt;K2,J2&lt;L2),J2,H2)</f>
+      <c r="O2">
+        <f ca="1">N2*1.3</f>
+        <v>309.80446144447</v>
+      </c>
+      <c r="P2">
+        <f ca="1">IF(OR(K2&gt;L2,K2&lt;N2),K2,H2)</f>
         <v>220.005332658</v>
       </c>
-      <c r="N2">
-        <f ca="1">IF(H2=M2,0,1)</f>
+      <c r="Q2">
+        <f ca="1">P2*1.3</f>
+        <v>286.0069324554</v>
+      </c>
+      <c r="R2">
+        <f ca="1">IF(H2=P2,0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1153,30 +1166,46 @@
         <v>229.7166</v>
       </c>
       <c r="I3">
+        <f ca="1" t="shared" ref="I3:I25" si="1">H3*1.3</f>
+        <v>298.63158</v>
+      </c>
+      <c r="J3">
         <v>1.021257</v>
       </c>
-      <c r="J3">
-        <f ca="1" t="shared" ref="J3:J25" si="1">H3*I3</f>
+      <c r="K3">
+        <f ca="1" t="shared" ref="K3:K25" si="2">H3*J3</f>
         <v>234.5996857662</v>
       </c>
-      <c r="K3">
-        <f ca="1" t="shared" ref="K3:K25" si="2">OFFSET($C$2,(ROW(C2)-1)*4,0)</f>
+      <c r="L3">
+        <f ca="1" t="shared" ref="L3:L25" si="3">OFFSET($C$2,(ROW(C2)-1)*4,0)</f>
         <v>217.727448319024</v>
       </c>
-      <c r="L3">
-        <f ca="1" t="shared" ref="L3:L25" si="3">OFFSET($D$2,(ROW(D2)-1)*4,0)</f>
+      <c r="M3">
+        <f ca="1" t="shared" ref="M3:M25" si="4">L3*1.3</f>
+        <v>283.045682814731</v>
+      </c>
+      <c r="N3">
+        <f ca="1" t="shared" ref="N3:N25" si="5">OFFSET($D$2,(ROW(D2)-1)*4,0)</f>
         <v>241.705751680976</v>
       </c>
-      <c r="M3">
-        <f ca="1" t="shared" ref="M3:M25" si="4">IF(OR(J3&gt;K3,J3&lt;L3),J3,H3)</f>
+      <c r="O3">
+        <f ca="1" t="shared" ref="O3:O25" si="6">N3*1.3</f>
+        <v>314.217477185269</v>
+      </c>
+      <c r="P3">
+        <f ca="1" t="shared" ref="P3:P25" si="7">IF(OR(K3&gt;L3,K3&lt;N3),K3,H3)</f>
         <v>234.5996857662</v>
       </c>
-      <c r="N3">
-        <f ca="1" t="shared" ref="N3:N25" si="5">IF(H3=M3,0,1)</f>
+      <c r="Q3">
+        <f ca="1" t="shared" ref="Q3:Q25" si="8">P3*1.3</f>
+        <v>304.97959149606</v>
+      </c>
+      <c r="R3">
+        <f ca="1" t="shared" ref="R3:R25" si="9">IF(H3=P3,0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1197,30 +1226,46 @@
         <v>225.547757142857</v>
       </c>
       <c r="I4">
+        <f ca="1" t="shared" si="1"/>
+        <v>293.212084285714</v>
+      </c>
+      <c r="J4">
         <v>0.997038</v>
-      </c>
-      <c r="J4">
-        <f ca="1" t="shared" si="1"/>
-        <v>224.8796846862</v>
       </c>
       <c r="K4">
         <f ca="1" t="shared" si="2"/>
-        <v>215.513381989471</v>
+        <v>224.8796846862</v>
       </c>
       <c r="L4">
         <f ca="1" t="shared" si="3"/>
-        <v>235.582132296243</v>
+        <v>215.513381989471</v>
       </c>
       <c r="M4">
         <f ca="1" t="shared" si="4"/>
-        <v>224.8796846862</v>
+        <v>280.167396586312</v>
       </c>
       <c r="N4">
         <f ca="1" t="shared" si="5"/>
+        <v>235.582132296243</v>
+      </c>
+      <c r="O4">
+        <f ca="1" t="shared" si="6"/>
+        <v>306.256771985116</v>
+      </c>
+      <c r="P4">
+        <f ca="1" t="shared" si="7"/>
+        <v>224.8796846862</v>
+      </c>
+      <c r="Q4">
+        <f ca="1" t="shared" si="8"/>
+        <v>292.34359009206</v>
+      </c>
+      <c r="R4">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1241,30 +1286,46 @@
         <v>219.725528571429</v>
       </c>
       <c r="I5">
+        <f ca="1" t="shared" si="1"/>
+        <v>285.643187142858</v>
+      </c>
+      <c r="J5">
         <v>1.03662</v>
-      </c>
-      <c r="J5">
-        <f ca="1" t="shared" si="1"/>
-        <v>227.771877427714</v>
       </c>
       <c r="K5">
         <f ca="1" t="shared" si="2"/>
-        <v>206.365200652347</v>
+        <v>227.771877427715</v>
       </c>
       <c r="L5">
         <f ca="1" t="shared" si="3"/>
-        <v>233.08585649051</v>
+        <v>206.365200652347</v>
       </c>
       <c r="M5">
         <f ca="1" t="shared" si="4"/>
-        <v>227.771877427714</v>
+        <v>268.274760848051</v>
       </c>
       <c r="N5">
         <f ca="1" t="shared" si="5"/>
+        <v>233.08585649051</v>
+      </c>
+      <c r="O5">
+        <f ca="1" t="shared" si="6"/>
+        <v>303.011613437663</v>
+      </c>
+      <c r="P5">
+        <f ca="1" t="shared" si="7"/>
+        <v>227.771877427715</v>
+      </c>
+      <c r="Q5">
+        <f ca="1" t="shared" si="8"/>
+        <v>296.103440656029</v>
+      </c>
+      <c r="R5">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1285,30 +1346,46 @@
         <v>226.245085714286</v>
       </c>
       <c r="I6">
+        <f ca="1" t="shared" si="1"/>
+        <v>294.118611428572</v>
+      </c>
+      <c r="J6">
         <v>1.034074</v>
-      </c>
-      <c r="J6">
-        <f ca="1" t="shared" si="1"/>
-        <v>233.954160764914</v>
       </c>
       <c r="K6">
         <f ca="1" t="shared" si="2"/>
-        <v>216.341890055393</v>
+        <v>233.954160764915</v>
       </c>
       <c r="L6">
         <f ca="1" t="shared" si="3"/>
-        <v>236.148281373179</v>
+        <v>216.341890055393</v>
       </c>
       <c r="M6">
         <f ca="1" t="shared" si="4"/>
-        <v>233.954160764914</v>
+        <v>281.244457072011</v>
       </c>
       <c r="N6">
         <f ca="1" t="shared" si="5"/>
+        <v>236.148281373179</v>
+      </c>
+      <c r="O6">
+        <f ca="1" t="shared" si="6"/>
+        <v>306.992765785133</v>
+      </c>
+      <c r="P6">
+        <f ca="1" t="shared" si="7"/>
+        <v>233.954160764915</v>
+      </c>
+      <c r="Q6">
+        <f ca="1" t="shared" si="8"/>
+        <v>304.140408994389</v>
+      </c>
+      <c r="R6">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1329,30 +1406,46 @@
         <v>226.837757142857</v>
       </c>
       <c r="I7">
+        <f ca="1" t="shared" si="1"/>
+        <v>294.889084285714</v>
+      </c>
+      <c r="J7">
         <v>0.988478</v>
-      </c>
-      <c r="J7">
-        <f ca="1" t="shared" si="1"/>
-        <v>224.224132505057</v>
       </c>
       <c r="K7">
         <f ca="1" t="shared" si="2"/>
-        <v>213.451390768899</v>
+        <v>224.224132505057</v>
       </c>
       <c r="L7">
         <f ca="1" t="shared" si="3"/>
-        <v>240.224123516816</v>
+        <v>213.451390768899</v>
       </c>
       <c r="M7">
         <f ca="1" t="shared" si="4"/>
-        <v>224.224132505057</v>
+        <v>277.486807999569</v>
       </c>
       <c r="N7">
         <f ca="1" t="shared" si="5"/>
+        <v>240.224123516816</v>
+      </c>
+      <c r="O7">
+        <f ca="1" t="shared" si="6"/>
+        <v>312.291360571861</v>
+      </c>
+      <c r="P7">
+        <f ca="1" t="shared" si="7"/>
+        <v>224.224132505057</v>
+      </c>
+      <c r="Q7">
+        <f ca="1" t="shared" si="8"/>
+        <v>291.491372256574</v>
+      </c>
+      <c r="R7">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1373,30 +1466,46 @@
         <v>226.8111</v>
       </c>
       <c r="I8">
+        <f ca="1" t="shared" si="1"/>
+        <v>294.85443</v>
+      </c>
+      <c r="J8">
         <v>1.00025</v>
-      </c>
-      <c r="J8">
-        <f ca="1" t="shared" si="1"/>
-        <v>226.867802775</v>
       </c>
       <c r="K8">
         <f ca="1" t="shared" si="2"/>
-        <v>215.030309660018</v>
+        <v>226.867802775</v>
       </c>
       <c r="L8">
         <f ca="1" t="shared" si="3"/>
-        <v>238.591890339982</v>
+        <v>215.030309660018</v>
       </c>
       <c r="M8">
         <f ca="1" t="shared" si="4"/>
-        <v>226.867802775</v>
+        <v>279.539402558023</v>
       </c>
       <c r="N8">
         <f ca="1" t="shared" si="5"/>
+        <v>238.591890339982</v>
+      </c>
+      <c r="O8">
+        <f ca="1" t="shared" si="6"/>
+        <v>310.169457441977</v>
+      </c>
+      <c r="P8">
+        <f ca="1" t="shared" si="7"/>
+        <v>226.867802775</v>
+      </c>
+      <c r="Q8">
+        <f ca="1" t="shared" si="8"/>
+        <v>294.9281436075</v>
+      </c>
+      <c r="R8">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1417,30 +1526,46 @@
         <v>228.450814285714</v>
       </c>
       <c r="I9">
+        <f ca="1" t="shared" si="1"/>
+        <v>296.986058571428</v>
+      </c>
+      <c r="J9">
         <v>1.037387</v>
-      </c>
-      <c r="J9">
-        <f ca="1" t="shared" si="1"/>
-        <v>236.991904879414</v>
       </c>
       <c r="K9">
         <f ca="1" t="shared" si="2"/>
-        <v>215.264504009684</v>
+        <v>236.991904879414</v>
       </c>
       <c r="L9">
         <f ca="1" t="shared" si="3"/>
-        <v>241.637124561744</v>
+        <v>215.264504009684</v>
       </c>
       <c r="M9">
         <f ca="1" t="shared" si="4"/>
-        <v>236.991904879414</v>
+        <v>279.843855212589</v>
       </c>
       <c r="N9">
         <f ca="1" t="shared" si="5"/>
+        <v>241.637124561744</v>
+      </c>
+      <c r="O9">
+        <f ca="1" t="shared" si="6"/>
+        <v>314.128261930267</v>
+      </c>
+      <c r="P9">
+        <f ca="1" t="shared" si="7"/>
+        <v>236.991904879414</v>
+      </c>
+      <c r="Q9">
+        <f ca="1" t="shared" si="8"/>
+        <v>308.089476343238</v>
+      </c>
+      <c r="R9">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1461,30 +1586,46 @@
         <v>236.690185714286</v>
       </c>
       <c r="I10">
+        <f ca="1" t="shared" si="1"/>
+        <v>307.697241428572</v>
+      </c>
+      <c r="J10">
         <v>1.045036</v>
-      </c>
-      <c r="J10">
-        <f ca="1" t="shared" si="1"/>
-        <v>247.349764918114</v>
       </c>
       <c r="K10">
         <f ca="1" t="shared" si="2"/>
-        <v>222.937649136061</v>
+        <v>247.349764918115</v>
       </c>
       <c r="L10">
         <f ca="1" t="shared" si="3"/>
-        <v>250.442722292511</v>
+        <v>222.937649136061</v>
       </c>
       <c r="M10">
         <f ca="1" t="shared" si="4"/>
-        <v>247.349764918114</v>
+        <v>289.818943876879</v>
       </c>
       <c r="N10">
         <f ca="1" t="shared" si="5"/>
+        <v>250.442722292511</v>
+      </c>
+      <c r="O10">
+        <f ca="1" t="shared" si="6"/>
+        <v>325.575538980264</v>
+      </c>
+      <c r="P10">
+        <f ca="1" t="shared" si="7"/>
+        <v>247.349764918115</v>
+      </c>
+      <c r="Q10">
+        <f ca="1" t="shared" si="8"/>
+        <v>321.554694393549</v>
+      </c>
+      <c r="R10">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1505,30 +1646,46 @@
         <v>247.882585714286</v>
       </c>
       <c r="I11">
+        <f ca="1" t="shared" si="1"/>
+        <v>322.247361428572</v>
+      </c>
+      <c r="J11">
         <v>0.986436</v>
-      </c>
-      <c r="J11">
-        <f ca="1" t="shared" si="1"/>
-        <v>244.520306321657</v>
       </c>
       <c r="K11">
         <f ca="1" t="shared" si="2"/>
-        <v>234.490017306291</v>
+        <v>244.520306321657</v>
       </c>
       <c r="L11">
         <f ca="1" t="shared" si="3"/>
-        <v>261.27515412228</v>
+        <v>234.490017306291</v>
       </c>
       <c r="M11">
         <f ca="1" t="shared" si="4"/>
-        <v>244.520306321657</v>
+        <v>304.837022498178</v>
       </c>
       <c r="N11">
         <f ca="1" t="shared" si="5"/>
+        <v>261.27515412228</v>
+      </c>
+      <c r="O11">
+        <f ca="1" t="shared" si="6"/>
+        <v>339.657700358964</v>
+      </c>
+      <c r="P11">
+        <f ca="1" t="shared" si="7"/>
+        <v>244.520306321657</v>
+      </c>
+      <c r="Q11">
+        <f ca="1" t="shared" si="8"/>
+        <v>317.876398218155</v>
+      </c>
+      <c r="R11">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1549,30 +1706,46 @@
         <v>256.990714285714</v>
       </c>
       <c r="I12">
+        <f ca="1" t="shared" si="1"/>
+        <v>334.087928571428</v>
+      </c>
+      <c r="J12">
         <v>0.972533</v>
-      </c>
-      <c r="J12">
-        <f ca="1" t="shared" si="1"/>
-        <v>249.931950336429</v>
       </c>
       <c r="K12">
         <f ca="1" t="shared" si="2"/>
-        <v>246.736286437844</v>
+        <v>249.931950336428</v>
       </c>
       <c r="L12">
         <f ca="1" t="shared" si="3"/>
-        <v>267.245142133585</v>
+        <v>246.736286437844</v>
       </c>
       <c r="M12">
         <f ca="1" t="shared" si="4"/>
-        <v>249.931950336429</v>
+        <v>320.757172369197</v>
       </c>
       <c r="N12">
         <f ca="1" t="shared" si="5"/>
+        <v>267.245142133585</v>
+      </c>
+      <c r="O12">
+        <f ca="1" t="shared" si="6"/>
+        <v>347.41868477366</v>
+      </c>
+      <c r="P12">
+        <f ca="1" t="shared" si="7"/>
+        <v>249.931950336428</v>
+      </c>
+      <c r="Q12">
+        <f ca="1" t="shared" si="8"/>
+        <v>324.911535437357</v>
+      </c>
+      <c r="R12">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1593,30 +1766,46 @@
         <v>267.715714285714</v>
       </c>
       <c r="I13">
+        <f ca="1" t="shared" si="1"/>
+        <v>348.030428571428</v>
+      </c>
+      <c r="J13">
         <v>1.006938</v>
-      </c>
-      <c r="J13">
-        <f ca="1" t="shared" si="1"/>
-        <v>269.573125911429</v>
       </c>
       <c r="K13">
         <f ca="1" t="shared" si="2"/>
-        <v>254.171917111817</v>
+        <v>269.573125911428</v>
       </c>
       <c r="L13">
         <f ca="1" t="shared" si="3"/>
-        <v>281.259511459612</v>
+        <v>254.171917111817</v>
       </c>
       <c r="M13">
         <f ca="1" t="shared" si="4"/>
-        <v>269.573125911429</v>
+        <v>330.423492245362</v>
       </c>
       <c r="N13">
         <f ca="1" t="shared" si="5"/>
+        <v>281.259511459612</v>
+      </c>
+      <c r="O13">
+        <f ca="1" t="shared" si="6"/>
+        <v>365.637364897496</v>
+      </c>
+      <c r="P13">
+        <f ca="1" t="shared" si="7"/>
+        <v>269.573125911428</v>
+      </c>
+      <c r="Q13">
+        <f ca="1" t="shared" si="8"/>
+        <v>350.445063684857</v>
+      </c>
+      <c r="R13">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1637,30 +1826,46 @@
         <v>263.390357142857</v>
       </c>
       <c r="I14">
+        <f ca="1" t="shared" si="1"/>
+        <v>342.407464285714</v>
+      </c>
+      <c r="J14">
         <v>1.024603</v>
-      </c>
-      <c r="J14">
-        <f ca="1" t="shared" si="1"/>
-        <v>269.870550099643</v>
       </c>
       <c r="K14">
         <f ca="1" t="shared" si="2"/>
-        <v>243.452379702952</v>
+        <v>269.870550099643</v>
       </c>
       <c r="L14">
         <f ca="1" t="shared" si="3"/>
-        <v>283.328334582762</v>
+        <v>243.452379702952</v>
       </c>
       <c r="M14">
         <f ca="1" t="shared" si="4"/>
-        <v>269.870550099643</v>
+        <v>316.488093613838</v>
       </c>
       <c r="N14">
         <f ca="1" t="shared" si="5"/>
+        <v>283.328334582762</v>
+      </c>
+      <c r="O14">
+        <f ca="1" t="shared" si="6"/>
+        <v>368.326834957591</v>
+      </c>
+      <c r="P14">
+        <f ca="1" t="shared" si="7"/>
+        <v>269.870550099643</v>
+      </c>
+      <c r="Q14">
+        <f ca="1" t="shared" si="8"/>
+        <v>350.831715129535</v>
+      </c>
+      <c r="R14">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1681,30 +1886,46 @@
         <v>263.116157142857</v>
       </c>
       <c r="I15">
+        <f ca="1" t="shared" si="1"/>
+        <v>342.051004285714</v>
+      </c>
+      <c r="J15">
         <v>0.985</v>
-      </c>
-      <c r="J15">
-        <f ca="1" t="shared" si="1"/>
-        <v>259.169414785714</v>
       </c>
       <c r="K15">
         <f ca="1" t="shared" si="2"/>
-        <v>242.786565717581</v>
+        <v>259.169414785714</v>
       </c>
       <c r="L15">
         <f ca="1" t="shared" si="3"/>
-        <v>283.445748568134</v>
+        <v>242.786565717581</v>
       </c>
       <c r="M15">
         <f ca="1" t="shared" si="4"/>
-        <v>259.169414785714</v>
+        <v>315.622535432855</v>
       </c>
       <c r="N15">
         <f ca="1" t="shared" si="5"/>
+        <v>283.445748568134</v>
+      </c>
+      <c r="O15">
+        <f ca="1" t="shared" si="6"/>
+        <v>368.479473138574</v>
+      </c>
+      <c r="P15">
+        <f ca="1" t="shared" si="7"/>
+        <v>259.169414785714</v>
+      </c>
+      <c r="Q15">
+        <f ca="1" t="shared" si="8"/>
+        <v>336.920239221428</v>
+      </c>
+      <c r="R15">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1725,30 +1946,46 @@
         <v>257.034942857143</v>
       </c>
       <c r="I16">
+        <f ca="1" t="shared" si="1"/>
+        <v>334.145425714286</v>
+      </c>
+      <c r="J16">
         <v>0.989829</v>
-      </c>
-      <c r="J16">
-        <f ca="1" t="shared" si="1"/>
-        <v>254.420640453343</v>
       </c>
       <c r="K16">
         <f ca="1" t="shared" si="2"/>
-        <v>243.610180948611</v>
+        <v>254.420640453343</v>
       </c>
       <c r="L16">
         <f ca="1" t="shared" si="3"/>
-        <v>270.459704765675</v>
+        <v>243.610180948611</v>
       </c>
       <c r="M16">
         <f ca="1" t="shared" si="4"/>
-        <v>254.420640453343</v>
+        <v>316.693235233194</v>
       </c>
       <c r="N16">
         <f ca="1" t="shared" si="5"/>
+        <v>270.459704765675</v>
+      </c>
+      <c r="O16">
+        <f ca="1" t="shared" si="6"/>
+        <v>351.597616195377</v>
+      </c>
+      <c r="P16">
+        <f ca="1" t="shared" si="7"/>
+        <v>254.420640453343</v>
+      </c>
+      <c r="Q16">
+        <f ca="1" t="shared" si="8"/>
+        <v>330.746832589346</v>
+      </c>
+      <c r="R16">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1769,30 +2006,46 @@
         <v>262.041728571429</v>
       </c>
       <c r="I17">
+        <f ca="1" t="shared" si="1"/>
+        <v>340.654247142858</v>
+      </c>
+      <c r="J17">
         <v>0.997796</v>
-      </c>
-      <c r="J17">
-        <f ca="1" t="shared" si="1"/>
-        <v>261.464188601657</v>
       </c>
       <c r="K17">
         <f ca="1" t="shared" si="2"/>
-        <v>245.496413725377</v>
+        <v>261.464188601658</v>
       </c>
       <c r="L17">
         <f ca="1" t="shared" si="3"/>
-        <v>278.58704341748</v>
+        <v>245.496413725377</v>
       </c>
       <c r="M17">
         <f ca="1" t="shared" si="4"/>
-        <v>261.464188601657</v>
+        <v>319.14533784299</v>
       </c>
       <c r="N17">
         <f ca="1" t="shared" si="5"/>
+        <v>278.58704341748</v>
+      </c>
+      <c r="O17">
+        <f ca="1" t="shared" si="6"/>
+        <v>362.163156442724</v>
+      </c>
+      <c r="P17">
+        <f ca="1" t="shared" si="7"/>
+        <v>261.464188601658</v>
+      </c>
+      <c r="Q17">
+        <f ca="1" t="shared" si="8"/>
+        <v>339.903445182155</v>
+      </c>
+      <c r="R17">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1813,30 +2066,46 @@
         <v>250.0026</v>
       </c>
       <c r="I18">
+        <f ca="1" t="shared" si="1"/>
+        <v>325.00338</v>
+      </c>
+      <c r="J18">
         <v>0.964075</v>
-      </c>
-      <c r="J18">
-        <f ca="1" t="shared" si="1"/>
-        <v>241.021256595</v>
       </c>
       <c r="K18">
         <f ca="1" t="shared" si="2"/>
-        <v>231.462251990685</v>
+        <v>241.021256595</v>
       </c>
       <c r="L18">
         <f ca="1" t="shared" si="3"/>
-        <v>268.542948009315</v>
+        <v>231.462251990685</v>
       </c>
       <c r="M18">
         <f ca="1" t="shared" si="4"/>
-        <v>241.021256595</v>
+        <v>300.900927587891</v>
       </c>
       <c r="N18">
         <f ca="1" t="shared" si="5"/>
+        <v>268.542948009315</v>
+      </c>
+      <c r="O18">
+        <f ca="1" t="shared" si="6"/>
+        <v>349.10583241211</v>
+      </c>
+      <c r="P18">
+        <f ca="1" t="shared" si="7"/>
+        <v>241.021256595</v>
+      </c>
+      <c r="Q18">
+        <f ca="1" t="shared" si="8"/>
+        <v>313.3276335735</v>
+      </c>
+      <c r="R18">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1857,30 +2126,46 @@
         <v>246.431314285714</v>
       </c>
       <c r="I19">
+        <f ca="1" t="shared" si="1"/>
+        <v>320.360708571428</v>
+      </c>
+      <c r="J19">
         <v>0.964811</v>
-      </c>
-      <c r="J19">
-        <f ca="1" t="shared" si="1"/>
-        <v>237.759642767314</v>
       </c>
       <c r="K19">
         <f ca="1" t="shared" si="2"/>
-        <v>228.224677142321</v>
+        <v>237.759642767314</v>
       </c>
       <c r="L19">
         <f ca="1" t="shared" si="3"/>
-        <v>264.637951429107</v>
+        <v>228.224677142321</v>
       </c>
       <c r="M19">
         <f ca="1" t="shared" si="4"/>
-        <v>237.759642767314</v>
+        <v>296.692080285017</v>
       </c>
       <c r="N19">
         <f ca="1" t="shared" si="5"/>
+        <v>264.637951429107</v>
+      </c>
+      <c r="O19">
+        <f ca="1" t="shared" si="6"/>
+        <v>344.029336857839</v>
+      </c>
+      <c r="P19">
+        <f ca="1" t="shared" si="7"/>
+        <v>237.759642767314</v>
+      </c>
+      <c r="Q19">
+        <f ca="1" t="shared" si="8"/>
+        <v>309.087535597508</v>
+      </c>
+      <c r="R19">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1901,30 +2186,46 @@
         <v>249.502671428571</v>
       </c>
       <c r="I20">
+        <f ca="1" t="shared" si="1"/>
+        <v>324.353472857142</v>
+      </c>
+      <c r="J20">
         <v>1.033227</v>
-      </c>
-      <c r="J20">
-        <f ca="1" t="shared" si="1"/>
-        <v>257.792896692129</v>
       </c>
       <c r="K20">
         <f ca="1" t="shared" si="2"/>
-        <v>237.179624921128</v>
+        <v>257.792896692128</v>
       </c>
       <c r="L20">
         <f ca="1" t="shared" si="3"/>
-        <v>261.825717936015</v>
+        <v>237.179624921128</v>
       </c>
       <c r="M20">
         <f ca="1" t="shared" si="4"/>
-        <v>257.792896692129</v>
+        <v>308.333512397466</v>
       </c>
       <c r="N20">
         <f ca="1" t="shared" si="5"/>
+        <v>261.825717936015</v>
+      </c>
+      <c r="O20">
+        <f ca="1" t="shared" si="6"/>
+        <v>340.37343331682</v>
+      </c>
+      <c r="P20">
+        <f ca="1" t="shared" si="7"/>
+        <v>257.792896692128</v>
+      </c>
+      <c r="Q20">
+        <f ca="1" t="shared" si="8"/>
+        <v>335.130765699767</v>
+      </c>
+      <c r="R20">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1945,30 +2246,46 @@
         <v>247.894114285714</v>
       </c>
       <c r="I21">
+        <f ca="1" t="shared" si="1"/>
+        <v>322.262348571428</v>
+      </c>
+      <c r="J21">
         <v>1.031367</v>
-      </c>
-      <c r="J21">
-        <f ca="1" t="shared" si="1"/>
-        <v>255.669808968514</v>
       </c>
       <c r="K21">
         <f ca="1" t="shared" si="2"/>
-        <v>233.495800290306</v>
+        <v>255.669808968514</v>
       </c>
       <c r="L21">
         <f ca="1" t="shared" si="3"/>
-        <v>262.292428281122</v>
+        <v>233.495800290306</v>
       </c>
       <c r="M21">
         <f ca="1" t="shared" si="4"/>
-        <v>255.669808968514</v>
+        <v>303.544540377398</v>
       </c>
       <c r="N21">
         <f ca="1" t="shared" si="5"/>
+        <v>262.292428281122</v>
+      </c>
+      <c r="O21">
+        <f ca="1" t="shared" si="6"/>
+        <v>340.980156765459</v>
+      </c>
+      <c r="P21">
+        <f ca="1" t="shared" si="7"/>
+        <v>255.669808968514</v>
+      </c>
+      <c r="Q21">
+        <f ca="1" t="shared" si="8"/>
+        <v>332.370751659068</v>
+      </c>
+      <c r="R21">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1989,30 +2306,46 @@
         <v>243.287571428571</v>
       </c>
       <c r="I22">
+        <f ca="1" t="shared" si="1"/>
+        <v>316.273842857142</v>
+      </c>
+      <c r="J22">
         <v>0.963888</v>
-      </c>
-      <c r="J22">
-        <f ca="1" t="shared" si="1"/>
-        <v>234.501970649143</v>
       </c>
       <c r="K22">
         <f ca="1" t="shared" si="2"/>
-        <v>224.964776659725</v>
+        <v>234.501970649142</v>
       </c>
       <c r="L22">
         <f ca="1" t="shared" si="3"/>
-        <v>261.610366197418</v>
+        <v>224.964776659725</v>
       </c>
       <c r="M22">
         <f ca="1" t="shared" si="4"/>
-        <v>234.501970649143</v>
+        <v>292.454209657643</v>
       </c>
       <c r="N22">
         <f ca="1" t="shared" si="5"/>
+        <v>261.610366197418</v>
+      </c>
+      <c r="O22">
+        <f ca="1" t="shared" si="6"/>
+        <v>340.093476056643</v>
+      </c>
+      <c r="P22">
+        <f ca="1" t="shared" si="7"/>
+        <v>234.501970649142</v>
+      </c>
+      <c r="Q22">
+        <f ca="1" t="shared" si="8"/>
+        <v>304.852561843885</v>
+      </c>
+      <c r="R22">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2033,30 +2366,46 @@
         <v>234.794528571429</v>
       </c>
       <c r="I23">
+        <f ca="1" t="shared" si="1"/>
+        <v>305.232887142858</v>
+      </c>
+      <c r="J23">
         <v>0.956548</v>
-      </c>
-      <c r="J23">
-        <f ca="1" t="shared" si="1"/>
-        <v>224.592236715943</v>
       </c>
       <c r="K23">
         <f ca="1" t="shared" si="2"/>
-        <v>220.353556136656</v>
+        <v>224.592236715943</v>
       </c>
       <c r="L23">
         <f ca="1" t="shared" si="3"/>
-        <v>249.235501006202</v>
+        <v>220.353556136656</v>
       </c>
       <c r="M23">
         <f ca="1" t="shared" si="4"/>
-        <v>224.592236715943</v>
+        <v>286.459622977653</v>
       </c>
       <c r="N23">
         <f ca="1" t="shared" si="5"/>
+        <v>249.235501006202</v>
+      </c>
+      <c r="O23">
+        <f ca="1" t="shared" si="6"/>
+        <v>324.006151308063</v>
+      </c>
+      <c r="P23">
+        <f ca="1" t="shared" si="7"/>
+        <v>224.592236715943</v>
+      </c>
+      <c r="Q23">
+        <f ca="1" t="shared" si="8"/>
+        <v>291.969907730726</v>
+      </c>
+      <c r="R23">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2077,30 +2426,46 @@
         <v>228.370157142857</v>
       </c>
       <c r="I24">
+        <f ca="1" t="shared" si="1"/>
+        <v>296.881204285714</v>
+      </c>
+      <c r="J24">
         <v>0.971773</v>
-      </c>
-      <c r="J24">
-        <f ca="1" t="shared" si="1"/>
-        <v>221.923952717186</v>
       </c>
       <c r="K24">
         <f ca="1" t="shared" si="2"/>
-        <v>212.043401141062</v>
+        <v>221.923952717186</v>
       </c>
       <c r="L24">
         <f ca="1" t="shared" si="3"/>
-        <v>244.696913144652</v>
+        <v>212.043401141062</v>
       </c>
       <c r="M24">
         <f ca="1" t="shared" si="4"/>
-        <v>221.923952717186</v>
+        <v>275.656421483381</v>
       </c>
       <c r="N24">
         <f ca="1" t="shared" si="5"/>
+        <v>244.696913144652</v>
+      </c>
+      <c r="O24">
+        <f ca="1" t="shared" si="6"/>
+        <v>318.105987088048</v>
+      </c>
+      <c r="P24">
+        <f ca="1" t="shared" si="7"/>
+        <v>221.923952717186</v>
+      </c>
+      <c r="Q24">
+        <f ca="1" t="shared" si="8"/>
+        <v>288.501138532341</v>
+      </c>
+      <c r="R24">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2121,26 +2486,42 @@
         <v>222.7209</v>
       </c>
       <c r="I25">
+        <f ca="1" t="shared" si="1"/>
+        <v>289.53717</v>
+      </c>
+      <c r="J25">
         <v>0.975908</v>
-      </c>
-      <c r="J25">
-        <f ca="1" t="shared" si="1"/>
-        <v>217.3551080772</v>
       </c>
       <c r="K25">
         <f ca="1" t="shared" si="2"/>
-        <v>210.026512726732</v>
+        <v>217.3551080772</v>
       </c>
       <c r="L25">
         <f ca="1" t="shared" si="3"/>
-        <v>235.415287273268</v>
+        <v>210.026512726732</v>
       </c>
       <c r="M25">
         <f ca="1" t="shared" si="4"/>
-        <v>217.3551080772</v>
+        <v>273.034466544752</v>
       </c>
       <c r="N25">
         <f ca="1" t="shared" si="5"/>
+        <v>235.415287273268</v>
+      </c>
+      <c r="O25">
+        <f ca="1" t="shared" si="6"/>
+        <v>306.039873455248</v>
+      </c>
+      <c r="P25">
+        <f ca="1" t="shared" si="7"/>
+        <v>217.3551080772</v>
+      </c>
+      <c r="Q25">
+        <f ca="1" t="shared" si="8"/>
+        <v>282.56164050036</v>
+      </c>
+      <c r="R25">
+        <f ca="1" t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
